--- a/data/stx_xlsx/ATRLJb.ST.xlsx
+++ b/data/stx_xlsx/ATRLJb.ST.xlsx
@@ -10162,24 +10162,78 @@
       <c r="E39" s="18">
         <v>31.06</v>
       </c>
-      <c r="F39" s="16"/>
-      <c r="G39" s="16"/>
-      <c r="H39" s="16"/>
-      <c r="I39" s="16"/>
-      <c r="J39" s="16"/>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
-      <c r="N39" s="16"/>
-      <c r="O39" s="16"/>
-      <c r="P39" s="16"/>
-      <c r="Q39" s="16"/>
-      <c r="R39" s="16"/>
-      <c r="S39" s="16"/>
-      <c r="T39" s="16"/>
-      <c r="U39" s="16"/>
-      <c r="V39" s="16"/>
-      <c r="W39" s="16"/>
+      <c r="F39" s="18">
+        <f t="shared" ref="F39:W39" si="1">SUM(F40:F41)</f>
+        <v>31.18</v>
+      </c>
+      <c r="G39" s="18">
+        <f t="shared" si="1"/>
+        <v>30.28</v>
+      </c>
+      <c r="H39" s="18">
+        <f t="shared" si="1"/>
+        <v>33.76</v>
+      </c>
+      <c r="I39" s="18">
+        <f t="shared" si="1"/>
+        <v>31.23</v>
+      </c>
+      <c r="J39" s="18">
+        <f t="shared" si="1"/>
+        <v>28.01</v>
+      </c>
+      <c r="K39" s="18">
+        <f t="shared" si="1"/>
+        <v>18.97</v>
+      </c>
+      <c r="L39" s="18">
+        <f t="shared" si="1"/>
+        <v>18.95</v>
+      </c>
+      <c r="M39" s="18">
+        <f t="shared" si="1"/>
+        <v>16.77</v>
+      </c>
+      <c r="N39" s="18">
+        <f t="shared" si="1"/>
+        <v>15.92</v>
+      </c>
+      <c r="O39" s="18">
+        <f t="shared" si="1"/>
+        <v>16.78</v>
+      </c>
+      <c r="P39" s="18">
+        <f t="shared" si="1"/>
+        <v>20.65</v>
+      </c>
+      <c r="Q39" s="18">
+        <f t="shared" si="1"/>
+        <v>9.03</v>
+      </c>
+      <c r="R39" s="18">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S39" s="18">
+        <f t="shared" si="1"/>
+        <v>12.4</v>
+      </c>
+      <c r="T39" s="18">
+        <f t="shared" si="1"/>
+        <v>7.99</v>
+      </c>
+      <c r="U39" s="18">
+        <f t="shared" si="1"/>
+        <v>7.02</v>
+      </c>
+      <c r="V39" s="18">
+        <f t="shared" si="1"/>
+        <v>4.72</v>
+      </c>
+      <c r="W39" s="18">
+        <f t="shared" si="1"/>
+        <v>4.33</v>
+      </c>
     </row>
     <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="14" t="s">
